--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11060,6 +11060,27 @@
       <c r="E506" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="C507" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="D507" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17077,6 +17098,16 @@
       </c>
       <c r="B600" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -17245,28 +17276,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2379336221069429</v>
+        <v>0.2353392813846219</v>
       </c>
       <c r="J2" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K2" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05859858487480007</v>
+        <v>0.05751678032505736</v>
       </c>
       <c r="M2" t="n">
-        <v>5.912752261444407</v>
+        <v>5.91609092140536</v>
       </c>
       <c r="N2" t="n">
-        <v>54.49767060799874</v>
+        <v>54.49085066769126</v>
       </c>
       <c r="O2" t="n">
-        <v>7.382253762097233</v>
+        <v>7.381791833131794</v>
       </c>
       <c r="P2" t="n">
-        <v>323.4055564422695</v>
+        <v>323.4311537447192</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17323,28 +17354,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.209297805426895</v>
+        <v>0.2042444714309903</v>
       </c>
       <c r="J3" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K3" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06339571782126163</v>
+        <v>0.06022298062863407</v>
       </c>
       <c r="M3" t="n">
-        <v>5.067734499471308</v>
+        <v>5.087694960305384</v>
       </c>
       <c r="N3" t="n">
-        <v>38.77967397669047</v>
+        <v>39.08578838062631</v>
       </c>
       <c r="O3" t="n">
-        <v>6.227332814029652</v>
+        <v>6.251862792850329</v>
       </c>
       <c r="P3" t="n">
-        <v>314.7466639891023</v>
+        <v>314.7965231758929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17401,28 +17432,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5325480895626342</v>
+        <v>0.52586719228312</v>
       </c>
       <c r="J4" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1878868751842265</v>
+        <v>0.1833018515240108</v>
       </c>
       <c r="M4" t="n">
-        <v>6.84668036003167</v>
+        <v>6.873905362115211</v>
       </c>
       <c r="N4" t="n">
-        <v>73.45414989078803</v>
+        <v>73.97799481353499</v>
       </c>
       <c r="O4" t="n">
-        <v>8.570539649916336</v>
+        <v>8.601046146460034</v>
       </c>
       <c r="P4" t="n">
-        <v>341.5331706083148</v>
+        <v>341.5990882986273</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17460,7 +17491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E506"/>
+  <dimension ref="A1:E507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31125,6 +31156,33 @@
         </is>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-34.966535251509654,173.65299239396674</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-34.96676640824995,173.65386453590241</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-34.96657646706014,173.6547947587701</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11081,6 +11081,48 @@
       <c r="E507" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>321.96</v>
+      </c>
+      <c r="C508" t="n">
+        <v>306.19</v>
+      </c>
+      <c r="D508" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>321.04</v>
+      </c>
+      <c r="C509" t="n">
+        <v>305.92</v>
+      </c>
+      <c r="D509" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17108,6 +17150,26 @@
       </c>
       <c r="B601" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -17276,28 +17338,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2353392813846219</v>
+        <v>0.2294869774498517</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05751678032505736</v>
+        <v>0.05501425947769634</v>
       </c>
       <c r="M2" t="n">
-        <v>5.91609092140536</v>
+        <v>5.926408967563487</v>
       </c>
       <c r="N2" t="n">
-        <v>54.49085066769126</v>
+        <v>54.53485406097395</v>
       </c>
       <c r="O2" t="n">
-        <v>7.381791833131794</v>
+        <v>7.384771767696951</v>
       </c>
       <c r="P2" t="n">
-        <v>323.4311537447192</v>
+        <v>323.4890561202142</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17354,28 +17416,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2042444714309903</v>
+        <v>0.194086418208584</v>
       </c>
       <c r="J3" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06022298062863407</v>
+        <v>0.05409575479416184</v>
       </c>
       <c r="M3" t="n">
-        <v>5.087694960305384</v>
+        <v>5.128160459275612</v>
       </c>
       <c r="N3" t="n">
-        <v>39.08578838062631</v>
+        <v>39.70839744457273</v>
       </c>
       <c r="O3" t="n">
-        <v>6.251862792850329</v>
+        <v>6.301459945486659</v>
       </c>
       <c r="P3" t="n">
-        <v>314.7965231758929</v>
+        <v>314.8970237802557</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17432,28 +17494,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.52586719228312</v>
+        <v>0.5093902964428507</v>
       </c>
       <c r="J4" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K4" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1833018515240108</v>
+        <v>0.1711961113267977</v>
       </c>
       <c r="M4" t="n">
-        <v>6.873905362115211</v>
+        <v>6.947684149114982</v>
       </c>
       <c r="N4" t="n">
-        <v>73.97799481353499</v>
+        <v>75.72988538194419</v>
       </c>
       <c r="O4" t="n">
-        <v>8.601046146460034</v>
+        <v>8.702291961428562</v>
       </c>
       <c r="P4" t="n">
-        <v>341.5990882986273</v>
+        <v>341.7621058750521</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17491,7 +17553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31183,6 +31245,60 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-34.96654008965178,173.65299172661054</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-34.9667673937979,173.65386439996584</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-34.96661445547625,173.65478951932639</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-34.966548332412394,173.6529905896331</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-34.966769812870126,173.65386406630336</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-34.96661983119547,173.6547887778953</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11123,6 +11123,69 @@
       <c r="E509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>318.79</v>
+      </c>
+      <c r="C510" t="n">
+        <v>305.14</v>
+      </c>
+      <c r="D510" t="n">
+        <v>324.93</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="C511" t="n">
+        <v>305.62</v>
+      </c>
+      <c r="D511" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="C512" t="n">
+        <v>305.76</v>
+      </c>
+      <c r="D512" t="n">
+        <v>328.18</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17170,6 +17233,36 @@
       </c>
       <c r="B603" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -17338,28 +17431,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2294869774498517</v>
+        <v>0.2185072870320696</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05501425947769634</v>
+        <v>0.05016583810469155</v>
       </c>
       <c r="M2" t="n">
-        <v>5.926408967563487</v>
+        <v>5.954886939993798</v>
       </c>
       <c r="N2" t="n">
-        <v>54.53485406097395</v>
+        <v>54.82668299134792</v>
       </c>
       <c r="O2" t="n">
-        <v>7.384771767696951</v>
+        <v>7.404504236702679</v>
       </c>
       <c r="P2" t="n">
-        <v>323.4890561202142</v>
+        <v>323.5981060837126</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17416,28 +17509,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.194086418208584</v>
+        <v>0.1785847533654078</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05409575479416184</v>
+        <v>0.0453757227140974</v>
       </c>
       <c r="M3" t="n">
-        <v>5.128160459275612</v>
+        <v>5.189363903900787</v>
       </c>
       <c r="N3" t="n">
-        <v>39.70839744457273</v>
+        <v>40.69284790449191</v>
       </c>
       <c r="O3" t="n">
-        <v>6.301459945486659</v>
+        <v>6.379094599117645</v>
       </c>
       <c r="P3" t="n">
-        <v>314.8970237802557</v>
+        <v>315.050989794903</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17494,28 +17587,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5093902964428507</v>
+        <v>0.4791185279373458</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1711961113267977</v>
+        <v>0.1483275176749289</v>
       </c>
       <c r="M4" t="n">
-        <v>6.947684149114982</v>
+        <v>7.096828232310856</v>
       </c>
       <c r="N4" t="n">
-        <v>75.72988538194419</v>
+        <v>79.93872683461689</v>
       </c>
       <c r="O4" t="n">
-        <v>8.702291961428562</v>
+        <v>8.940845979806211</v>
       </c>
       <c r="P4" t="n">
-        <v>341.7621058750521</v>
+        <v>342.0627633495456</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17553,7 +17646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31299,6 +31392,87 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.96656849133775,173.65298780898092</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.96677680130098,173.65386310238932</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.966685504564715,173.6547797200716</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.96656571388582,173.6529881920931</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.96677250072815,173.6538636955672</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.966662568163045,173.65478288351497</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.966558367077475,173.6529892054864</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.96677124639441,173.6538638685774</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.96665638608601,173.65478373616153</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11184,6 +11184,27 @@
         <v>328.18</v>
       </c>
       <c r="E512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>320.36</v>
+      </c>
+      <c r="C513" t="n">
+        <v>305.56</v>
+      </c>
+      <c r="D513" t="n">
+        <v>330.1</v>
+      </c>
+      <c r="E513" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11200,7 +11221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B606"/>
+  <dimension ref="A1:B607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17263,6 +17284,16 @@
       </c>
       <c r="B606" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -17431,28 +17462,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2185072870320696</v>
+        <v>0.2153012505504908</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05016583810469155</v>
+        <v>0.04882430595010923</v>
       </c>
       <c r="M2" t="n">
-        <v>5.954886939993798</v>
+        <v>5.961758062088672</v>
       </c>
       <c r="N2" t="n">
-        <v>54.82668299134792</v>
+        <v>54.87800183934627</v>
       </c>
       <c r="O2" t="n">
-        <v>7.404504236702679</v>
+        <v>7.407968806585667</v>
       </c>
       <c r="P2" t="n">
-        <v>323.5981060837126</v>
+        <v>323.6300166005381</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17509,28 +17540,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1785847533654078</v>
+        <v>0.1735364901229285</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0453757227140974</v>
+        <v>0.04272200388661596</v>
       </c>
       <c r="M3" t="n">
-        <v>5.189363903900787</v>
+        <v>5.208803581166217</v>
       </c>
       <c r="N3" t="n">
-        <v>40.69284790449191</v>
+        <v>41.00611255813834</v>
       </c>
       <c r="O3" t="n">
-        <v>6.379094599117645</v>
+        <v>6.403601530243613</v>
       </c>
       <c r="P3" t="n">
-        <v>315.050989794903</v>
+        <v>315.1012364748966</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17587,28 +17618,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4791185279373458</v>
+        <v>0.4703658941508005</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1483275176749289</v>
+        <v>0.14241105640621</v>
       </c>
       <c r="M4" t="n">
-        <v>7.096828232310856</v>
+        <v>7.139088026968134</v>
       </c>
       <c r="N4" t="n">
-        <v>79.93872683461689</v>
+        <v>80.96319395955436</v>
       </c>
       <c r="O4" t="n">
-        <v>8.940845979806211</v>
+        <v>8.99795498763771</v>
       </c>
       <c r="P4" t="n">
-        <v>342.0627633495456</v>
+        <v>342.1498805951904</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17646,7 +17677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31473,6 +31504,33 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.966554424887626,173.65298974925838</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.96677303829975,173.65386362142</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.96663918378463,173.65478610874266</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11205,6 +11205,48 @@
         <v>330.1</v>
       </c>
       <c r="E513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>316.37</v>
+      </c>
+      <c r="C514" t="n">
+        <v>307.08</v>
+      </c>
+      <c r="D514" t="n">
+        <v>339.89</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>315.96</v>
+      </c>
+      <c r="C515" t="n">
+        <v>307.22</v>
+      </c>
+      <c r="D515" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="E515" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11221,7 +11263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17294,6 +17336,26 @@
       </c>
       <c r="B607" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -17462,28 +17524,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2153012505504908</v>
+        <v>0.2059611409488954</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04882430595010923</v>
+        <v>0.04468406517103807</v>
       </c>
       <c r="M2" t="n">
-        <v>5.961758062088672</v>
+        <v>5.992938064435038</v>
       </c>
       <c r="N2" t="n">
-        <v>54.87800183934627</v>
+        <v>55.33399191788835</v>
       </c>
       <c r="O2" t="n">
-        <v>7.407968806585667</v>
+        <v>7.438682135828117</v>
       </c>
       <c r="P2" t="n">
-        <v>323.6300166005381</v>
+        <v>323.7234429080697</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17540,28 +17602,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1735364901229285</v>
+        <v>0.1646402732168483</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04272200388661596</v>
+        <v>0.03836580462040118</v>
       </c>
       <c r="M3" t="n">
-        <v>5.208803581166217</v>
+        <v>5.240040749300178</v>
       </c>
       <c r="N3" t="n">
-        <v>41.00611255813834</v>
+        <v>41.45384533505503</v>
       </c>
       <c r="O3" t="n">
-        <v>6.403601530243613</v>
+        <v>6.438466070039899</v>
       </c>
       <c r="P3" t="n">
-        <v>315.1012364748966</v>
+        <v>315.190221520811</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17618,28 +17680,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4703658941508005</v>
+        <v>0.4601663960094087</v>
       </c>
       <c r="J4" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K4" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L4" t="n">
-        <v>0.14241105640621</v>
+        <v>0.1369108188475299</v>
       </c>
       <c r="M4" t="n">
-        <v>7.139088026968134</v>
+        <v>7.176836613898876</v>
       </c>
       <c r="N4" t="n">
-        <v>80.96319395955436</v>
+        <v>81.44694246117585</v>
       </c>
       <c r="O4" t="n">
-        <v>8.99795498763771</v>
+        <v>9.024795978922507</v>
       </c>
       <c r="P4" t="n">
-        <v>342.1498805951904</v>
+        <v>342.2519005658305</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17677,7 +17739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31531,6 +31593,60 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.96659017338177,173.65298481823356</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.96675941981908,173.6538654998162</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.96655146996537,173.65479820642045</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.96659384678591,173.65298431153656</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.96675816548533,173.65386567282636</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.96654492950683,173.65479910849348</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E515"/>
+  <dimension ref="A1:E519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11249,6 +11249,90 @@
       <c r="E515" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>316.39</v>
+      </c>
+      <c r="C516" t="n">
+        <v>307.47</v>
+      </c>
+      <c r="D516" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="C517" t="n">
+        <v>307.42</v>
+      </c>
+      <c r="D517" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="C518" t="n">
+        <v>307.41</v>
+      </c>
+      <c r="D518" t="n">
+        <v>352.12</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="C519" t="n">
+        <v>307.36</v>
+      </c>
+      <c r="D519" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B609"/>
+  <dimension ref="A1:B613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17356,6 +17440,46 @@
       </c>
       <c r="B609" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -17524,28 +17648,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2059611409488954</v>
+        <v>0.1859630929531696</v>
       </c>
       <c r="J2" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04468406517103807</v>
+        <v>0.03630707597962157</v>
       </c>
       <c r="M2" t="n">
-        <v>5.992938064435038</v>
+        <v>6.062536609247299</v>
       </c>
       <c r="N2" t="n">
-        <v>55.33399191788835</v>
+        <v>56.45729045406746</v>
       </c>
       <c r="O2" t="n">
-        <v>7.438682135828117</v>
+        <v>7.51380665535569</v>
       </c>
       <c r="P2" t="n">
-        <v>323.7234429080697</v>
+        <v>323.9246091946726</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17602,28 +17726,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1646402732168483</v>
+        <v>0.147632234281343</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03836580462040118</v>
+        <v>0.03075208165926013</v>
       </c>
       <c r="M3" t="n">
-        <v>5.240040749300178</v>
+        <v>5.297280985683917</v>
       </c>
       <c r="N3" t="n">
-        <v>41.45384533505503</v>
+        <v>42.25147319648626</v>
       </c>
       <c r="O3" t="n">
-        <v>6.438466070039899</v>
+        <v>6.500113321818802</v>
       </c>
       <c r="P3" t="n">
-        <v>315.190221520811</v>
+        <v>315.3612997128756</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17680,28 +17804,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4601663960094087</v>
+        <v>0.4530363851654036</v>
       </c>
       <c r="J4" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1369108188475299</v>
+        <v>0.1347182702246731</v>
       </c>
       <c r="M4" t="n">
-        <v>7.176836613898876</v>
+        <v>7.167088245682621</v>
       </c>
       <c r="N4" t="n">
-        <v>81.44694246117585</v>
+        <v>81.08048095570392</v>
       </c>
       <c r="O4" t="n">
-        <v>9.024795978922507</v>
+        <v>9.004470054128889</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2519005658305</v>
+        <v>342.323574265256</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17739,7 +17863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E515"/>
+  <dimension ref="A1:E519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31647,6 +31771,114 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.96658999419131,173.6529848429505</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.966755925603636,173.653865981773</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.96650989773564,173.65480394014278</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-34.966607644450214,173.65298240833278</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-34.96675637357997,173.6538659199837</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-34.966460172330926,173.65481079835956</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-34.966607644450214,173.65298240833278</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-34.96675646317524,173.6538659076258</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-34.96644189488468,173.65481331921563</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-34.966607644450214,173.65298240833278</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-34.966756911151585,173.6538658458365</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-34.96645175037041,173.65481195993064</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11331,6 +11331,48 @@
         <v>351.02</v>
       </c>
       <c r="E519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="C520" t="n">
+        <v>307.04</v>
+      </c>
+      <c r="D520" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>314.95</v>
+      </c>
+      <c r="C521" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="D521" t="n">
+        <v>346.77</v>
+      </c>
+      <c r="E521" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11347,7 +11389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B613"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17480,6 +17522,26 @@
       </c>
       <c r="B613" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -17648,28 +17710,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1859630929531696</v>
+        <v>0.1759826651327596</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03630707597962157</v>
+        <v>0.032447997012781</v>
       </c>
       <c r="M2" t="n">
-        <v>6.062536609247299</v>
+        <v>6.097579001371198</v>
       </c>
       <c r="N2" t="n">
-        <v>56.45729045406746</v>
+        <v>57.02498276085412</v>
       </c>
       <c r="O2" t="n">
-        <v>7.51380665535569</v>
+        <v>7.551488777774494</v>
       </c>
       <c r="P2" t="n">
-        <v>323.9246091946726</v>
+        <v>324.0253493260064</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17726,28 +17788,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.147632234281343</v>
+        <v>0.1393683908052552</v>
       </c>
       <c r="J3" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K3" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03075208165926013</v>
+        <v>0.02736717215264606</v>
       </c>
       <c r="M3" t="n">
-        <v>5.297280985683917</v>
+        <v>5.32510610472203</v>
       </c>
       <c r="N3" t="n">
-        <v>42.25147319648626</v>
+        <v>42.62717277546467</v>
       </c>
       <c r="O3" t="n">
-        <v>6.500113321818802</v>
+        <v>6.52894882622499</v>
       </c>
       <c r="P3" t="n">
-        <v>315.3612997128756</v>
+        <v>315.4447126855265</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17804,28 +17866,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4530363851654036</v>
+        <v>0.4479387096016352</v>
       </c>
       <c r="J4" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1347182702246731</v>
+        <v>0.1327081644679834</v>
       </c>
       <c r="M4" t="n">
-        <v>7.167088245682621</v>
+        <v>7.172848012900745</v>
       </c>
       <c r="N4" t="n">
-        <v>81.08048095570392</v>
+        <v>80.97365883770757</v>
       </c>
       <c r="O4" t="n">
-        <v>9.004470054128889</v>
+        <v>8.998536483101438</v>
       </c>
       <c r="P4" t="n">
-        <v>342.323574265256</v>
+        <v>342.3750335635758</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17863,7 +17925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31879,6 +31941,60 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-34.966610153116434,173.65298206229565</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-34.96675977820014,173.6538654503847</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-34.96648355671053,173.65480757314506</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-34.966602895903414,173.65298306333153</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-34.9667529689598,173.65386638958262</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-34.96648982838319,173.65480670814472</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0038/nzd0038.xlsx
+++ b/data/nzd0038/nzd0038.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E521"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11373,6 +11373,90 @@
         <v>346.77</v>
       </c>
       <c r="E521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>318.74</v>
+      </c>
+      <c r="C522" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="D522" t="n">
+        <v>347.33</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="C523" t="n">
+        <v>308.37</v>
+      </c>
+      <c r="D523" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="C524" t="n">
+        <v>308.55</v>
+      </c>
+      <c r="D524" t="n">
+        <v>349.33</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="C525" t="n">
+        <v>308.94</v>
+      </c>
+      <c r="D525" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="E525" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11389,7 +11473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17542,6 +17626,46 @@
       </c>
       <c r="B615" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -17710,28 +17834,28 @@
         <v>0.0842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1759826651327596</v>
+        <v>0.16840484765917</v>
       </c>
       <c r="J2" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.032447997012781</v>
+        <v>0.03009939664936767</v>
       </c>
       <c r="M2" t="n">
-        <v>6.097579001371198</v>
+        <v>6.095784049563808</v>
       </c>
       <c r="N2" t="n">
-        <v>57.02498276085412</v>
+        <v>56.87723816444667</v>
       </c>
       <c r="O2" t="n">
-        <v>7.551488777774494</v>
+        <v>7.541699951897229</v>
       </c>
       <c r="P2" t="n">
-        <v>324.0253493260064</v>
+        <v>324.1021906235138</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17788,28 +17912,28 @@
         <v>0.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1393683908052552</v>
+        <v>0.1247154890463228</v>
       </c>
       <c r="J3" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02736717215264606</v>
+        <v>0.02193954284496613</v>
       </c>
       <c r="M3" t="n">
-        <v>5.32510610472203</v>
+        <v>5.369503889654623</v>
       </c>
       <c r="N3" t="n">
-        <v>42.62717277546467</v>
+        <v>43.1557628387782</v>
       </c>
       <c r="O3" t="n">
-        <v>6.52894882622499</v>
+        <v>6.569304593241069</v>
       </c>
       <c r="P3" t="n">
-        <v>315.4447126855265</v>
+        <v>315.5933285457168</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17866,28 +17990,28 @@
         <v>0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4479387096016352</v>
+        <v>0.4405737662051806</v>
       </c>
       <c r="J4" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1327081644679834</v>
+        <v>0.1303781477389133</v>
       </c>
       <c r="M4" t="n">
-        <v>7.172848012900745</v>
+        <v>7.165835751793292</v>
       </c>
       <c r="N4" t="n">
-        <v>80.97365883770757</v>
+        <v>80.57916964563127</v>
       </c>
       <c r="O4" t="n">
-        <v>8.998536483101438</v>
+        <v>8.976590090097201</v>
       </c>
       <c r="P4" t="n">
-        <v>342.3750335635758</v>
+        <v>342.4497296583549</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17925,7 +18049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E521"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31995,6 +32119,114 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-34.966568939313866,173.65298774718863</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-34.96675010191122,173.65386678503432</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-34.966484811045056,173.65480740014502</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-34.96652584401108,173.65299369160363</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-34.96674786202953,173.65386709398095</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-34.96646035152158,173.65481077364527</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-34.96651957234536,173.6529945566947</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-34.966746249314696,173.6538673164225</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-34.96646689198025,173.65480987157395</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-34.96650075734811,173.6529971519672</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-34.96674275509924,173.6538677983792</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-34.96646572724104,173.6548100322168</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
